--- a/tableau-synthese-lisa-rupert.xlsx
+++ b/tableau-synthese-lisa-rupert.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liselotte\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liselotte\Desktop\Portfolio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{421DDEA1-9EBF-41E2-9D91-D9575DD99B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5833DB-7916-4709-82F0-639E864832EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="96" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -50,19 +39,10 @@
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Option :</t>
   </si>
   <si>
     <t>▢ SISR</t>
-  </si>
-  <si>
-    <t>▢ SLAM</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio :</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -238,6 +218,39 @@
 Application du principe du moindre privilège.
 Sécurisation du portail client (authentification, gestion des permissions, cloisonnement des données).
 Ce portail client accessible en ligne permet aux clients de consulter leurs interventions, leur parc d’équipements et les informations associées. Il améliore l’autonomie des clients, fluidifie la relation client et renforce la présence numérique de l’entreprise en proposant un service digital sécurisé.</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://lisarupert03.github.io/portfolio-lisa-rupert/</t>
+  </si>
+  <si>
+    <t>N° candidat : 02423418735</t>
+  </si>
+  <si>
+    <t>x SLAM</t>
+  </si>
+  <si>
+    <t>Développement d’une application web de gestion (site e-commerce de livres)
+Conception d’une base de données MySQL.
+Développement du back-end avec Node.js et Express.
+Création d’une API REST.
+Développement du front-end en HTML, CSS, JavaScript.
+Gestion des utilisateurs et des commandes.
+Tests des fonctionnalités via Postman.</t>
+  </si>
+  <si>
+    <t>Développement d’une application desktop en JavaFX
+Création d’une interface graphique avec JavaFX.
+Implémentation des fonctionnalités métier en Java.
+Connexion à une base de données.
+Gestion des événements utilisateurs.
+Tests et validation des fonctionnalités.</t>
+  </si>
+  <si>
+    <t>Janv 2026 - Avril 2026</t>
+  </si>
+  <si>
+    <t>Fév 2026 -
+Avril 2026</t>
   </si>
 </sst>
 </file>
@@ -780,15 +793,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -821,42 +870,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1177,124 +1190,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="43"/>
+      <c r="A3" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="34"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="A4" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="B6" s="43" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="D6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="D7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="E7" s="20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="20" t="s">
+      <c r="F7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>18</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>21</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1333,16 +1346,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="A8" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1381,26 +1394,26 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="44" t="s">
         <v>27</v>
       </c>
+      <c r="B9" s="22" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1440,21 +1453,21 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10"/>
@@ -1495,22 +1508,22 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="164.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1548,14 +1561,28 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="168" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1592,15 +1619,27 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
+      <c r="D13" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="F13" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1863,16 +1902,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="A19" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="42"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1911,24 +1950,24 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1967,25 +2006,25 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>36</v>
+      <c r="A21" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2249,16 +2288,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="A27" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2296,23 +2335,23 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="44" t="s">
-        <v>35</v>
+      <c r="A28" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>32</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2352,28 +2391,28 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="222" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2729,11 +2768,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2741,6 +2775,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2751,21 +2790,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003AD845D0F00B92468DFF472C0C367C9C" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b465b386f622b531418bd500e70b03a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b6a58e55-5a49-49f3-9ec1-4b0581f13459" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d081952ca132371ed5f1ead6897c8a46" ns2:_="">
     <xsd:import namespace="b6a58e55-5a49-49f3-9ec1-4b0581f13459"/>
@@ -2909,24 +2933,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48547B5C-4ED6-4F98-96BB-40089B423D9C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A7E4A9-6A97-4866-8C01-AE418C38B582}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B503CC11-C859-4604-92B7-962DC0559F71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2942,4 +2964,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A7E4A9-6A97-4866-8C01-AE418C38B582}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48547B5C-4ED6-4F98-96BB-40089B423D9C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tableau-synthese-lisa-rupert.xlsx
+++ b/tableau-synthese-lisa-rupert.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liselotte\Desktop\Portfolio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5833DB-7916-4709-82F0-639E864832EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7FDA5A-D2F5-4171-A917-58256C6DA57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="96" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -251,6 +248,12 @@
   <si>
     <t>Fév 2026 -
 Avril 2026</t>
+  </si>
+  <si>
+    <t>Fev 2025</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
   </si>
 </sst>
 </file>
@@ -728,7 +731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -805,9 +808,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -832,44 +874,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1190,124 +1196,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="34"/>
+      <c r="A3" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
+      <c r="A4" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="B6" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="F7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>17</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>18</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1346,16 +1352,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
+      <c r="A8" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1394,26 +1400,26 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1453,21 +1459,23 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="C10" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10"/>
@@ -1508,22 +1516,24 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="164.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="B11" s="48">
+        <v>45717</v>
+      </c>
       <c r="C11" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1563,25 +1573,25 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1621,24 +1631,24 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1902,16 +1912,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
+      <c r="A19" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1950,24 +1960,24 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -2007,24 +2017,24 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2288,16 +2298,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
+      <c r="A27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2336,22 +2346,22 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="22" t="s">
         <v>31</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>32</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2391,28 +2401,28 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="222" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2768,6 +2778,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2775,11 +2790,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2790,6 +2800,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003AD845D0F00B92468DFF472C0C367C9C" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b465b386f622b531418bd500e70b03a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b6a58e55-5a49-49f3-9ec1-4b0581f13459" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d081952ca132371ed5f1ead6897c8a46" ns2:_="">
     <xsd:import namespace="b6a58e55-5a49-49f3-9ec1-4b0581f13459"/>
@@ -2933,22 +2958,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48547B5C-4ED6-4F98-96BB-40089B423D9C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A7E4A9-6A97-4866-8C01-AE418C38B582}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B503CC11-C859-4604-92B7-962DC0559F71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2964,21 +2991,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A7E4A9-6A97-4866-8C01-AE418C38B582}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48547B5C-4ED6-4F98-96BB-40089B423D9C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>